--- a/advantest/dist/20261022_Advantest模型_v0.1.xlsx
+++ b/advantest/dist/20261022_Advantest模型_v0.1.xlsx
@@ -11237,7 +11237,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/equipment/dist/20261022_</t>
+      <t xml:space="preserve">markets/equipment/dist/20261023_</t>
     </r>
     <r>
       <rPr>
@@ -11256,7 +11256,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.1.1.xlsx</t>
+      <t xml:space="preserve">_v0.1.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -11732,7 +11732,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/equipment/dist/20261022_</t>
+      <t xml:space="preserve">markets/equipment/dist/20261023_</t>
     </r>
     <r>
       <rPr>
@@ -11751,7 +11751,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.1.1.xlsx</t>
+      <t xml:space="preserve">_v0.1.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -12187,7 +12187,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/equipment/dist/20261022_</t>
+      <t xml:space="preserve">markets/equipment/dist/20261023_</t>
     </r>
     <r>
       <rPr>
@@ -12206,7 +12206,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.1.1.xlsx</t>
+      <t xml:space="preserve">_v0.1.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -12595,7 +12595,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/equipment/dist/20261022_</t>
+      <t xml:space="preserve">markets/equipment/dist/20261023_</t>
     </r>
     <r>
       <rPr>
@@ -12614,7 +12614,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.1.1.xlsx</t>
+      <t xml:space="preserve">_v0.1.2.xlsx</t>
     </r>
     <r>
       <rPr>
